--- a/data/memories/memory_01/locales/es/documents/reception/Emergency_Contacts.xlsx
+++ b/data/memories/memory_01/locales/es/documents/reception/Emergency_Contacts.xlsx
@@ -433,7 +433,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Emergency Contacts</t>
+          <t>Contactos de emergencia</t>
         </is>
       </c>
     </row>
@@ -445,7 +445,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>Interno</t>
         </is>
       </c>
     </row>
@@ -469,33 +469,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Reception</t>
+          <t>Recepción</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Internal Contacts</t>
+          <t>Contactos Internos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Servicio</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Extension</t>
+          <t>Extensión</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Reception</t>
+          <t>Recepción</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT Support</t>
+          <t>Soporte de TI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -531,7 +531,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Seguridad</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
